--- a/测试集/泛用性验收_v3/F23/F23_条件格式验证.xlsx
+++ b/测试集/泛用性验收_v3/F23/F23_条件格式验证.xlsx
@@ -72,11 +72,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -496,7 +497,7 @@
           <t>CF001</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,7 +505,7 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46037</v>
       </c>
     </row>
@@ -522,7 +523,7 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46068</v>
       </c>
     </row>
@@ -540,7 +541,7 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>46096</v>
       </c>
     </row>
@@ -558,7 +559,7 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>46127</v>
       </c>
     </row>
@@ -576,7 +577,7 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>46157</v>
       </c>
     </row>
@@ -594,7 +595,7 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>46188</v>
       </c>
     </row>
@@ -612,7 +613,7 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -630,7 +631,7 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>46249</v>
       </c>
     </row>
@@ -648,10 +649,13 @@
       <formula>DATE(2026,10,1)-D2&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="数值超出范围" error="请输入1-100的整数" type="whole" operator="between">
-      <formula1>1</formula1>
-      <formula2>100</formula2>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="数值超出范围" error="请输入0~1之间的小数" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="B2:B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="自定义验证失败" error="完成率必须是0~1之间的数字" type="custom">
+      <formula1>AND(B2&gt;=0,B2&lt;=1,ISNUMBER(B2))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
